--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXII/LTAIPT_A63F22.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXII/LTAIPT_A63F22.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>48973</t>
   </si>
@@ -254,7 +254,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -266,22 +266,19 @@
     <t>02/07/2018</t>
   </si>
   <si>
-    <t>30393A8883BDD815939963A266D3854F</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>03/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, no ha celebrado ningún financiamiento (Deuda Pública), sin embargo, en caso de existir la necesidad de un financiamiento, se deberá dar cumplimiento a los requisitos establecidos en los artículos 20, 21, 22, 23 y 24 de la Ley de Deuda Pública para el Estado de Tlaxcala y sus Municipios, además, de considerar lo establecido en la Ley de Disciplina Financiera de las Entidades Federativas y los Municipios, por lo anterior, no se presenta hipervínculo del informe consolidado y/o información financiera que representen la deuda pública de esta institución educativa.</t>
-  </si>
-  <si>
-    <t>6923BDA17BA43401ED3C87D855698A15</t>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>5ED117F6EC531A5C19104C248BD55613</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>02/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no ha celebrado ningún financiamiento (Deuda Pública), sin embargo, en caso de existir la necesidad de un financiamiento, se deberá dar cumplimiento a los requisitos establecidos en los artículos 20, 21, 22, 23 y 24 de la Ley de Deuda Pública para el Estado de Tlaxcala y sus Municipios, además, de considerar lo establecido en la Ley de Disciplina Financiera de las Entidades Federativas y los Municipios, por lo anterior, no se presenta hipervínculo del informe consolidado y/o información financiera que representen la deuda pública de esta institución educativa.</t>
   </si>
   <si>
     <t>Contratos de proyectos de prestación de servicios (PPS)</t>
@@ -689,10 +686,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1086,13 +1083,13 @@
     </row>
     <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>84</v>
@@ -1179,104 +1176,6 @@
         <v>81</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF9" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1291,7 +1190,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G190">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G196">
       <formula1>Hidden_16</formula1>
     </dataValidation>
   </dataValidations>
@@ -1306,27 +1205,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
